--- a/artfynd/A 16997-2024 artfynd.xlsx
+++ b/artfynd/A 16997-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118539270</v>
+        <v>118539237</v>
       </c>
       <c r="B2" t="n">
         <v>97846</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -731,14 +731,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandsjön ost 2, Vg</t>
+          <t>Sandsjön ost 1, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>350373</v>
+        <v>350393</v>
       </c>
       <c r="R2" t="n">
-        <v>6382354</v>
+        <v>6382351</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -803,7 +803,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118539237</v>
+        <v>118539295</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -838,7 +838,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,14 +859,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandsjön ost 1, Vg</t>
+          <t>Sandsjön ost 3, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>350393</v>
+        <v>350383</v>
       </c>
       <c r="R3" t="n">
-        <v>6382351</v>
+        <v>6382379</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -931,7 +931,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118539295</v>
+        <v>118539270</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -966,7 +966,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,14 +987,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandsjön ost 3, Vg</t>
+          <t>Sandsjön ost 2, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>350383</v>
+        <v>350373</v>
       </c>
       <c r="R4" t="n">
-        <v>6382379</v>
+        <v>6382354</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 16997-2024 artfynd.xlsx
+++ b/artfynd/A 16997-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118539295</v>
+        <v>118539270</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -838,7 +838,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,14 +859,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandsjön ost 3, Vg</t>
+          <t>Sandsjön ost 2, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>350383</v>
+        <v>350373</v>
       </c>
       <c r="R3" t="n">
-        <v>6382379</v>
+        <v>6382354</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -931,7 +931,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118539270</v>
+        <v>118539295</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -966,7 +966,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,14 +987,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandsjön ost 2, Vg</t>
+          <t>Sandsjön ost 3, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>350373</v>
+        <v>350383</v>
       </c>
       <c r="R4" t="n">
-        <v>6382354</v>
+        <v>6382379</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 16997-2024 artfynd.xlsx
+++ b/artfynd/A 16997-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118539237</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118539270</v>
+        <v>118539295</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,14 +859,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandsjön ost 2, Vg</t>
+          <t>Sandsjön ost 3, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>350373</v>
+        <v>350383</v>
       </c>
       <c r="R3" t="n">
-        <v>6382354</v>
+        <v>6382379</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -931,10 +931,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118539295</v>
+        <v>118539270</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,14 +987,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandsjön ost 3, Vg</t>
+          <t>Sandsjön ost 2, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>350383</v>
+        <v>350373</v>
       </c>
       <c r="R4" t="n">
-        <v>6382379</v>
+        <v>6382354</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 16997-2024 artfynd.xlsx
+++ b/artfynd/A 16997-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118539237</v>
+        <v>118539270</v>
       </c>
       <c r="B2" t="n">
         <v>97853</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -731,14 +731,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandsjön ost 1, Vg</t>
+          <t>Sandsjön ost 2, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>350393</v>
+        <v>350373</v>
       </c>
       <c r="R2" t="n">
-        <v>6382351</v>
+        <v>6382354</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -803,7 +803,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118539295</v>
+        <v>118539237</v>
       </c>
       <c r="B3" t="n">
         <v>97853</v>
@@ -838,7 +838,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,14 +859,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandsjön ost 3, Vg</t>
+          <t>Sandsjön ost 1, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>350383</v>
+        <v>350393</v>
       </c>
       <c r="R3" t="n">
-        <v>6382379</v>
+        <v>6382351</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -931,7 +931,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118539270</v>
+        <v>118539295</v>
       </c>
       <c r="B4" t="n">
         <v>97853</v>
@@ -966,7 +966,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,14 +987,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandsjön ost 2, Vg</t>
+          <t>Sandsjön ost 3, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>350373</v>
+        <v>350383</v>
       </c>
       <c r="R4" t="n">
-        <v>6382354</v>
+        <v>6382379</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 16997-2024 artfynd.xlsx
+++ b/artfynd/A 16997-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118539295</v>
+        <v>118539237</v>
       </c>
       <c r="B2" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -731,14 +726,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandsjön ost 3, Vg</t>
+          <t>Sandsjön ost 1, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>350383</v>
+        <v>350393</v>
       </c>
       <c r="R2" t="n">
-        <v>6382379</v>
+        <v>6382351</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -806,12 +801,7 @@
         <v>118539270</v>
       </c>
       <c r="B3" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,15 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118539237</v>
+        <v>118539295</v>
       </c>
       <c r="B4" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,7 +951,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,14 +972,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandsjön ost 1, Vg</t>
+          <t>Sandsjön ost 3, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>350393</v>
+        <v>350383</v>
       </c>
       <c r="R4" t="n">
-        <v>6382351</v>
+        <v>6382379</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
